--- a/checklist_forms/045_employee_screening_checklist--checklist_forms.xlsx
+++ b/checklist_forms/045_employee_screening_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>new_employee</t>
+          <t>employee_screening</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,190 +691,6 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>employee_status</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Employee Status</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>job_title_2</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Job Title</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>employment_type_2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Employment Type</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>date_of_birth_2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Date of Birth</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>hire_date_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Hire Date</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>termination_date_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Termination Date</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>employee_status_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Employee Status</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>job_title_3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Job Title</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -891,12 +707,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -941,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_active'}</t>
+          <t>not_active</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Not Active'}</t>
+          <t>Not Active</t>
         </is>
       </c>
     </row>
@@ -958,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -975,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -992,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1009,131 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'temporary'}</t>
+          <t>temporary</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Temporary'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>employee_status_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'active'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Active'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>employee_status_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'resigned'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Resigned'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>employee_status_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'terminated'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'Terminated'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>employment_type_2_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>employment_type_2_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>employee_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>employee_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Inactive</t>
+          <t>Temporary</t>
         </is>
       </c>
     </row>
